--- a/sources/data/fy26-code-reconciliation.xlsx
+++ b/sources/data/fy26-code-reconciliation.xlsx
@@ -3359,20 +3359,36 @@
       <c r="D78" s="12" t="n">
         <v>40000</v>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>no account of this amount</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr"/>
-      <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="8" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr"/>
-      <c r="J78" s="8" t="inlineStr"/>
-      <c r="K78" s="9" t="n"/>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>UNPAIRED</t>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>0100-3-301-2110-99-0-99-2-555027</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>CURR ADOPT</t>
+        </is>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>-4222.59</v>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>35777.41</v>
+      </c>
+      <c r="J78" s="12" t="n">
+        <v>43639.08</v>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>amount (approp)</t>
         </is>
       </c>
     </row>
@@ -3685,30 +3701,30 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="13" t="n"/>
-      <c r="B85" s="14" t="inlineStr">
+      <c r="A85" s="18" t="n"/>
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>TOTAL 2110</t>
         </is>
       </c>
-      <c r="C85" s="13" t="n"/>
-      <c r="D85" s="15" t="n">
+      <c r="C85" s="18" t="n"/>
+      <c r="D85" s="20" t="n">
         <v>463481</v>
       </c>
-      <c r="E85" s="13" t="n"/>
-      <c r="F85" s="13" t="n"/>
-      <c r="G85" s="15" t="n">
-        <v>423481.24</v>
-      </c>
-      <c r="H85" s="13" t="n"/>
-      <c r="I85" s="13" t="n"/>
-      <c r="J85" s="15" t="n">
-        <v>397615.87</v>
-      </c>
-      <c r="K85" s="13" t="n"/>
-      <c r="L85" s="16" t="inlineStr">
-        <is>
-          <t>differs by -40,000</t>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="20" t="n">
+        <v>463481.24</v>
+      </c>
+      <c r="H85" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="20" t="n">
+        <v>441254.95</v>
+      </c>
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="21" t="inlineStr">
+        <is>
+          <t>sums agree</t>
         </is>
       </c>
     </row>
@@ -22186,38 +22202,38 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>2110</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Special Education / System Curriculum Adop / Curriculum/Spec Ed Directors / Special Education Clerical</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="D13" s="26" t="n">
-        <v>11</v>
-      </c>
-      <c r="E13" s="27" t="n">
+      <c r="D13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>463481</v>
       </c>
-      <c r="F13" s="27" t="n">
-        <v>423481.24</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>397615.87</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-39999.76000000001</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="32" t="n">
+      <c r="F13" s="12" t="n">
+        <v>463481.24</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>441254.95</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0.2399999999906868</v>
+      </c>
+      <c r="I13" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23530,13 +23546,13 @@
         <v>26287475.93</v>
       </c>
       <c r="F50" s="36" t="n">
-        <v>26247474</v>
+        <v>26287474</v>
       </c>
       <c r="G50" s="36" t="n">
-        <v>25613679.23</v>
+        <v>25657318.30999999</v>
       </c>
       <c r="H50" s="36" t="n">
-        <v>-40001.93000000343</v>
+        <v>-1.930000003427267</v>
       </c>
       <c r="I50" s="18" t="n"/>
       <c r="J50" s="18" t="n"/>
